--- a/clientes.xlsx
+++ b/clientes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lmacias\Desktop\RUTAS LÓGICAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC60420B-5715-4AEF-9ECE-AD3F8303DFF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87B49469-3C53-4501-A467-1592618A5E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{740DF47F-2FF5-45E2-939D-94824F9E772D}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">clientes!$A$1:$K$98</definedName>
   </definedNames>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="290">
   <si>
     <t>XIMENA SARAHI LOPEZ VILLASEÑOR</t>
   </si>
@@ -646,6 +646,270 @@
   </si>
   <si>
     <t>AQUILES SERDAN 575 COLONIA SANTA ANITA TLAJOMULCO DE ZUÑIGA 45645</t>
+  </si>
+  <si>
+    <t>DAVID HORACIO CABRERA BRICEÑO</t>
+  </si>
+  <si>
+    <t>BLANCA DELIA PASOS RAMOS</t>
+  </si>
+  <si>
+    <t>PINTURAS RAVI</t>
+  </si>
+  <si>
+    <t>NOELIA COTA LOPEZ</t>
+  </si>
+  <si>
+    <t>DEILY CARMINA ROJO HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MANGUERAS Y SOLUCIONES INTEGRALES D PACIFICO</t>
+  </si>
+  <si>
+    <t>RANDALL ALBERTO COTA LEY</t>
+  </si>
+  <si>
+    <t>FRANCISCO CABANILLAS ORTIZ</t>
+  </si>
+  <si>
+    <t>HIRAM GERMAN NOGUERON MUNGUIA</t>
+  </si>
+  <si>
+    <t>JOSE DE LA CRUZ AMAVIZCA CHAVEZ</t>
+  </si>
+  <si>
+    <t>DESARROLLO COMERCIAL GRUJAC</t>
+  </si>
+  <si>
+    <t>YSABEL MAREZ CARDOZA</t>
+  </si>
+  <si>
+    <t>PINTURAS MARTINEZ INDA</t>
+  </si>
+  <si>
+    <t>MONICA RODRIGUEZ ALMADA</t>
+  </si>
+  <si>
+    <t>MANUEL DE JESUS MUÑOZ MENDIVIL</t>
+  </si>
+  <si>
+    <t>GASES Y EQUIPOS DE OBREGON</t>
+  </si>
+  <si>
+    <t>ANGELICA AYDEE AUDELO CRUZ</t>
+  </si>
+  <si>
+    <t>JORGE ALFONSO JACKSON CECEÑA</t>
+  </si>
+  <si>
+    <t>JUAN ALFONSO CABANILLAS FLORES</t>
+  </si>
+  <si>
+    <t>HECTOR ROJO INZUNZA</t>
+  </si>
+  <si>
+    <t>HERNAN BRASS HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MARIBEL RAMIREZ MARTINEZ</t>
+  </si>
+  <si>
+    <t>CARLOS ALEJANDRO FLORES INZUNZA</t>
+  </si>
+  <si>
+    <t>IVETH ALEJANDRA PAYAN LEYVA</t>
+  </si>
+  <si>
+    <t>ANDRES VALDEZ ANGUAMEA</t>
+  </si>
+  <si>
+    <t>MATERIALES GISO</t>
+  </si>
+  <si>
+    <t>JOZHE ALONSO LOPEZ HIGUERA</t>
+  </si>
+  <si>
+    <t>ROSARIO MONCERRAT PORTILLO HERNANDEZ</t>
+  </si>
+  <si>
+    <t>PLOMERIA MODERNA</t>
+  </si>
+  <si>
+    <t>MARIA NAVA LEON</t>
+  </si>
+  <si>
+    <t>LUIS ANTONIO SPENCER</t>
+  </si>
+  <si>
+    <t>ALMA CARMINA MACHADO COTA</t>
+  </si>
+  <si>
+    <t>JUAN ENRIQUE ARMENTA SEVILLA</t>
+  </si>
+  <si>
+    <t>JAVIER ROBLES BORBOA</t>
+  </si>
+  <si>
+    <t>ARLIN SARAHI LOPEZ REYES</t>
+  </si>
+  <si>
+    <t>MARTHA LIDIA ALCANTAR MIRANDA</t>
+  </si>
+  <si>
+    <t>ORALIA GIL GALAVIZ</t>
+  </si>
+  <si>
+    <t>CHRISTIAN ABIGAIL ROJO PACHECO</t>
+  </si>
+  <si>
+    <t>CAPSA MATERIALES</t>
+  </si>
+  <si>
+    <t>OLIVIA CAMACHO SUJA</t>
+  </si>
+  <si>
+    <t>GLORIA GALAVIZ BORQUEZ</t>
+  </si>
+  <si>
+    <t>JUAN MANUEL SANCHEZ CURIEL</t>
+  </si>
+  <si>
+    <t>REYNA EVELIA AVILA VERDUGO</t>
+  </si>
+  <si>
+    <t>NYSER ARMANDO LEOPOLDO GOMEZ COTA</t>
+  </si>
+  <si>
+    <t>IVAN ANTONIO HERNANDEZ ENRIQUEZ</t>
+  </si>
+  <si>
+    <t>ALMA YOLANDA SERRANO RAMOS</t>
+  </si>
+  <si>
+    <t>BACILIO CUADRAS INZUNZA</t>
+  </si>
+  <si>
+    <t>CHRISTIAN MIGUEL LOPEZ ORTEGA</t>
+  </si>
+  <si>
+    <t>JESUS ERNESTO ORDUÑO CAMPAS</t>
+  </si>
+  <si>
+    <t>RAUL ENRIQUE LEON BOJORQUEZ</t>
+  </si>
+  <si>
+    <t>JOSE ARAMBURO LIZARRAGA</t>
+  </si>
+  <si>
+    <t>VICTOR DAVID MARTINEZ RUIZ</t>
+  </si>
+  <si>
+    <t>ALBERTO VERDUGO DELGADILLO</t>
+  </si>
+  <si>
+    <t>DIANA LORENA MORENO ROBLES</t>
+  </si>
+  <si>
+    <t>FERRETERA LA CENTRAL DE CAJEME</t>
+  </si>
+  <si>
+    <t>MANUELA DE LA CRUZ BURGOS PARRA</t>
+  </si>
+  <si>
+    <t>MARIA DE LOS ANGELES COTA VEGA</t>
+  </si>
+  <si>
+    <t>CARLOS ARMANDO ALMODOVAR MORENO</t>
+  </si>
+  <si>
+    <t>TUBOS Y MANGUERAS FLEXIBLES DEL NOR</t>
+  </si>
+  <si>
+    <t>ELSA MARIA DUARTE COZARIT</t>
+  </si>
+  <si>
+    <t>REYNALDO PADILLA BELTRAN</t>
+  </si>
+  <si>
+    <t>PAZ TORRES</t>
+  </si>
+  <si>
+    <t>FERRETERIA Y COMERCIALIZADORA DEL NOROESTE</t>
+  </si>
+  <si>
+    <t>SERGIO CARLOS VEGA FELIX</t>
+  </si>
+  <si>
+    <t>VELIA EDITH CARRILLO SUAREZ</t>
+  </si>
+  <si>
+    <t>GUADALUPE ANGULO SANTILLANES</t>
+  </si>
+  <si>
+    <t>RAMON DE JESUS FLORES CAMACHO</t>
+  </si>
+  <si>
+    <t>GUADALUPE MARTINEZ ZAMORA</t>
+  </si>
+  <si>
+    <t>PINTURAS DE CAJEME</t>
+  </si>
+  <si>
+    <t>TANIA IVONNE MANCILLAS VALDEZ</t>
+  </si>
+  <si>
+    <t>EQUIPOS Y PARTES GLOBAL</t>
+  </si>
+  <si>
+    <t>PINTURAS ESPECIALES DE LOS MOCHIS</t>
+  </si>
+  <si>
+    <t>LAURA LYDIA MUY FLORES</t>
+  </si>
+  <si>
+    <t>FRANCISCO G RAMIREZ</t>
+  </si>
+  <si>
+    <t>SERGIO HUMBERTO RUBIO LOPEZ</t>
+  </si>
+  <si>
+    <t>JOHANA IVETTE VAZQUEZ MEDINA</t>
+  </si>
+  <si>
+    <t>YANKY AUTO SHOP</t>
+  </si>
+  <si>
+    <t>MANUEL TRINIDAD CHIN DUARTE</t>
+  </si>
+  <si>
+    <t>CARLOS ARMANDO CUADRAS CANO</t>
+  </si>
+  <si>
+    <t>JESUS MANUEL MARTINEZ LUGO</t>
+  </si>
+  <si>
+    <t>GILBERTO ENRIQUE GASTELUM ESPINOZA</t>
+  </si>
+  <si>
+    <t>KARLA GARNICA MELLOY</t>
+  </si>
+  <si>
+    <t>CARLOS MENDOZA LUNA</t>
+  </si>
+  <si>
+    <t>LOGISTICA ZARR</t>
+  </si>
+  <si>
+    <t>ROBERTO HINOJOSA NIEBLAS</t>
+  </si>
+  <si>
+    <t>MATILDE INZUNZA GUILLEN</t>
+  </si>
+  <si>
+    <t>ANAHY CAZAREZ ARMENTA</t>
+  </si>
+  <si>
+    <t>YASBEL GUADALUPE OCHOA DIAZ</t>
   </si>
 </sst>
 </file>
@@ -716,7 +980,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -731,12 +995,35 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1066,11 +1353,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1E63F05-B3C2-4FFE-ACBF-95CFEEB9BDFD}">
-  <dimension ref="A1:K98"/>
+  <dimension ref="A1:K186"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.90625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25.26953125" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.1796875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.54296875" style="6" bestFit="1" customWidth="1"/>
@@ -4304,8 +4591,979 @@
         <v>190</v>
       </c>
     </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A99">
+        <v>50000416</v>
+      </c>
+      <c r="B99" s="12">
+        <v>621795</v>
+      </c>
+      <c r="C99" s="13" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A100">
+        <v>50000416</v>
+      </c>
+      <c r="B100" s="12">
+        <v>621251</v>
+      </c>
+      <c r="C100" s="13" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A101">
+        <v>50000416</v>
+      </c>
+      <c r="B101" s="12">
+        <v>1046</v>
+      </c>
+      <c r="C101" s="13" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A102">
+        <v>50000416</v>
+      </c>
+      <c r="B102" s="12">
+        <v>621641</v>
+      </c>
+      <c r="C102" s="13" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A103">
+        <v>50000416</v>
+      </c>
+      <c r="B103" s="12">
+        <v>233979</v>
+      </c>
+      <c r="C103" s="14" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A104">
+        <v>50000416</v>
+      </c>
+      <c r="B104" s="12">
+        <v>235061</v>
+      </c>
+      <c r="C104" s="14" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A105">
+        <v>50000416</v>
+      </c>
+      <c r="B105" s="12">
+        <v>621509</v>
+      </c>
+      <c r="C105" s="13" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A106">
+        <v>50000416</v>
+      </c>
+      <c r="B106" s="12">
+        <v>620295</v>
+      </c>
+      <c r="C106" s="13" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A107">
+        <v>50000416</v>
+      </c>
+      <c r="B107" s="12">
+        <v>621886</v>
+      </c>
+      <c r="C107" s="13" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A108">
+        <v>50000416</v>
+      </c>
+      <c r="B108" s="12">
+        <v>621242</v>
+      </c>
+      <c r="C108" s="14" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A109">
+        <v>50000416</v>
+      </c>
+      <c r="B109" s="12">
+        <v>621780</v>
+      </c>
+      <c r="C109" s="14" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A110">
+        <v>50000416</v>
+      </c>
+      <c r="B110" s="12">
+        <v>620850</v>
+      </c>
+      <c r="C110" s="14" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A111">
+        <v>50000416</v>
+      </c>
+      <c r="B111" s="12">
+        <v>1508</v>
+      </c>
+      <c r="C111" s="14" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A112">
+        <v>50000416</v>
+      </c>
+      <c r="B112" s="12">
+        <v>234183</v>
+      </c>
+      <c r="C112" s="14" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A113">
+        <v>50000416</v>
+      </c>
+      <c r="B113" s="12">
+        <v>347182</v>
+      </c>
+      <c r="C113" s="14" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A114">
+        <v>50000416</v>
+      </c>
+      <c r="B114" s="12">
+        <v>621897</v>
+      </c>
+      <c r="C114" s="14" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A115">
+        <v>50000416</v>
+      </c>
+      <c r="B115" s="12">
+        <v>1000264</v>
+      </c>
+      <c r="C115" s="13" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A116">
+        <v>50000416</v>
+      </c>
+      <c r="B116" s="12">
+        <v>621608</v>
+      </c>
+      <c r="C116" s="13" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A117">
+        <v>50000416</v>
+      </c>
+      <c r="B117" s="12">
+        <v>621781</v>
+      </c>
+      <c r="C117" s="14" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A118">
+        <v>50000416</v>
+      </c>
+      <c r="B118" s="12">
+        <v>621845</v>
+      </c>
+      <c r="C118" s="14" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A119">
+        <v>50000416</v>
+      </c>
+      <c r="B119" s="12">
+        <v>621887</v>
+      </c>
+      <c r="C119" s="13" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A120">
+        <v>50000416</v>
+      </c>
+      <c r="B120" s="12">
+        <v>621316</v>
+      </c>
+      <c r="C120" s="14" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A121">
+        <v>50000416</v>
+      </c>
+      <c r="B121" s="12">
+        <v>620445</v>
+      </c>
+      <c r="C121" s="14" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A122">
+        <v>50000416</v>
+      </c>
+      <c r="B122" s="12">
+        <v>621596</v>
+      </c>
+      <c r="C122" s="14" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A123">
+        <v>50000416</v>
+      </c>
+      <c r="B123" s="12">
+        <v>340708</v>
+      </c>
+      <c r="C123" s="13" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A124">
+        <v>50000416</v>
+      </c>
+      <c r="B124" s="12">
+        <v>234382</v>
+      </c>
+      <c r="C124" s="13" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A125">
+        <v>50000416</v>
+      </c>
+      <c r="B125" s="12">
+        <v>341184</v>
+      </c>
+      <c r="C125" s="13" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A126">
+        <v>50000416</v>
+      </c>
+      <c r="B126" s="12">
+        <v>343306</v>
+      </c>
+      <c r="C126" s="13" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A127">
+        <v>50000416</v>
+      </c>
+      <c r="B127" s="12">
+        <v>621846</v>
+      </c>
+      <c r="C127" s="13" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A128">
+        <v>50000416</v>
+      </c>
+      <c r="B128" s="12">
+        <v>620782</v>
+      </c>
+      <c r="C128" s="14" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A129">
+        <v>50000416</v>
+      </c>
+      <c r="B129" s="12">
+        <v>621578</v>
+      </c>
+      <c r="C129" s="14" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A130">
+        <v>50000416</v>
+      </c>
+      <c r="B130" s="12">
+        <v>621404</v>
+      </c>
+      <c r="C130" s="14" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A131">
+        <v>50000416</v>
+      </c>
+      <c r="B131" s="12">
+        <v>346207</v>
+      </c>
+      <c r="C131" s="13" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A132">
+        <v>50000416</v>
+      </c>
+      <c r="B132" s="12">
+        <v>620292</v>
+      </c>
+      <c r="C132" s="13" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A133">
+        <v>50000416</v>
+      </c>
+      <c r="B133" s="12">
+        <v>621840</v>
+      </c>
+      <c r="C133" s="14" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A134">
+        <v>50000416</v>
+      </c>
+      <c r="B134" s="12">
+        <v>621459</v>
+      </c>
+      <c r="C134" s="14" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A135">
+        <v>50000416</v>
+      </c>
+      <c r="B135" s="12">
+        <v>235022</v>
+      </c>
+      <c r="C135" s="14" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A136">
+        <v>50000416</v>
+      </c>
+      <c r="B136" s="12">
+        <v>234255</v>
+      </c>
+      <c r="C136" s="13" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A137">
+        <v>50000416</v>
+      </c>
+      <c r="B137" s="12">
+        <v>621525</v>
+      </c>
+      <c r="C137" s="14" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A138">
+        <v>50000416</v>
+      </c>
+      <c r="B138" s="12">
+        <v>234840</v>
+      </c>
+      <c r="C138" s="14" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A139">
+        <v>50000416</v>
+      </c>
+      <c r="B139" s="12">
+        <v>235121</v>
+      </c>
+      <c r="C139" s="14" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A140">
+        <v>50000416</v>
+      </c>
+      <c r="B140" s="12">
+        <v>345366</v>
+      </c>
+      <c r="C140" s="14" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A141">
+        <v>50000416</v>
+      </c>
+      <c r="B141" s="12">
+        <v>234841</v>
+      </c>
+      <c r="C141" s="14" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A142">
+        <v>50000416</v>
+      </c>
+      <c r="B142" s="12">
+        <v>234791</v>
+      </c>
+      <c r="C142" s="14" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A143">
+        <v>50000416</v>
+      </c>
+      <c r="B143" s="12">
+        <v>234634</v>
+      </c>
+      <c r="C143" s="14" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A144">
+        <v>50000416</v>
+      </c>
+      <c r="B144" s="12">
+        <v>621799</v>
+      </c>
+      <c r="C144" s="14" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A145">
+        <v>50000416</v>
+      </c>
+      <c r="B145" s="12">
+        <v>342130</v>
+      </c>
+      <c r="C145" s="14" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A146">
+        <v>50000416</v>
+      </c>
+      <c r="B146" s="12">
+        <v>621787</v>
+      </c>
+      <c r="C146" s="14" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A147">
+        <v>50000416</v>
+      </c>
+      <c r="B147" s="12">
+        <v>621607</v>
+      </c>
+      <c r="C147" s="14" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A148">
+        <v>50000416</v>
+      </c>
+      <c r="B148" s="12">
+        <v>621675</v>
+      </c>
+      <c r="C148" s="14" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A149">
+        <v>50000416</v>
+      </c>
+      <c r="B149" s="12">
+        <v>621320</v>
+      </c>
+      <c r="C149" s="13" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A150">
+        <v>50000416</v>
+      </c>
+      <c r="B150" s="12">
+        <v>621900</v>
+      </c>
+      <c r="C150" s="13" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A151">
+        <v>50000416</v>
+      </c>
+      <c r="B151" s="12">
+        <v>1000263</v>
+      </c>
+      <c r="C151" s="14" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A152">
+        <v>50000416</v>
+      </c>
+      <c r="B152" s="12">
+        <v>346213</v>
+      </c>
+      <c r="C152" s="13" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A153">
+        <v>50000416</v>
+      </c>
+      <c r="B153" s="12">
+        <v>620567</v>
+      </c>
+      <c r="C153" s="14" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A154">
+        <v>50000416</v>
+      </c>
+      <c r="B154" s="12">
+        <v>621885</v>
+      </c>
+      <c r="C154" s="14" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A155">
+        <v>50000416</v>
+      </c>
+      <c r="B155" s="12">
+        <v>348080</v>
+      </c>
+      <c r="C155" s="14" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A156">
+        <v>50000416</v>
+      </c>
+      <c r="B156" s="12">
+        <v>621802</v>
+      </c>
+      <c r="C156" s="14" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A157">
+        <v>50000416</v>
+      </c>
+      <c r="B157" s="12">
+        <v>621834</v>
+      </c>
+      <c r="C157" s="14" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A158">
+        <v>50000416</v>
+      </c>
+      <c r="B158" s="12">
+        <v>621817</v>
+      </c>
+      <c r="C158" s="14" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A159">
+        <v>50000416</v>
+      </c>
+      <c r="B159" s="12">
+        <v>621796</v>
+      </c>
+      <c r="C159" s="14" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A160">
+        <v>50000416</v>
+      </c>
+      <c r="B160" s="12">
+        <v>621790</v>
+      </c>
+      <c r="C160" s="14" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A161">
+        <v>50000416</v>
+      </c>
+      <c r="B161" s="12">
+        <v>621903</v>
+      </c>
+      <c r="C161" s="13" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A162">
+        <v>50000416</v>
+      </c>
+      <c r="B162" s="12">
+        <v>621677</v>
+      </c>
+      <c r="C162" s="13" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A163">
+        <v>50000416</v>
+      </c>
+      <c r="B163" s="12">
+        <v>340315</v>
+      </c>
+      <c r="C163" s="14" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A164">
+        <v>50000416</v>
+      </c>
+      <c r="B164" s="12">
+        <v>172861</v>
+      </c>
+      <c r="C164" s="13" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A165">
+        <v>50000416</v>
+      </c>
+      <c r="B165" s="12">
+        <v>620935</v>
+      </c>
+      <c r="C165" s="13" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A166">
+        <v>50000416</v>
+      </c>
+      <c r="B166" s="12">
+        <v>347296</v>
+      </c>
+      <c r="C166" s="14" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A167">
+        <v>50000416</v>
+      </c>
+      <c r="B167" s="12">
+        <v>620942</v>
+      </c>
+      <c r="C167" s="14" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A168">
+        <v>50000416</v>
+      </c>
+      <c r="B168" s="12">
+        <v>621481</v>
+      </c>
+      <c r="C168" s="14" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A169">
+        <v>50000416</v>
+      </c>
+      <c r="B169" s="12">
+        <v>620834</v>
+      </c>
+      <c r="C169" s="14" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A170">
+        <v>50000416</v>
+      </c>
+      <c r="B170" s="12">
+        <v>620180</v>
+      </c>
+      <c r="C170" s="14" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A171">
+        <v>50000416</v>
+      </c>
+      <c r="B171" s="12">
+        <v>621601</v>
+      </c>
+      <c r="C171" s="13" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A172">
+        <v>50000416</v>
+      </c>
+      <c r="B172" s="12">
+        <v>620884</v>
+      </c>
+      <c r="C172" s="14" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A173">
+        <v>50000416</v>
+      </c>
+      <c r="B173" s="12">
+        <v>621454</v>
+      </c>
+      <c r="C173" s="14" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A174">
+        <v>50000416</v>
+      </c>
+      <c r="B174" s="12">
+        <v>621905</v>
+      </c>
+      <c r="C174" s="13" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A175">
+        <v>50000416</v>
+      </c>
+      <c r="B175" s="12">
+        <v>621804</v>
+      </c>
+      <c r="C175" s="14" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A176">
+        <v>50000416</v>
+      </c>
+      <c r="B176" s="12">
+        <v>347056</v>
+      </c>
+      <c r="C176" s="14" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A177">
+        <v>50000416</v>
+      </c>
+      <c r="B177" s="12">
+        <v>234177</v>
+      </c>
+      <c r="C177" s="13" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A178">
+        <v>50000416</v>
+      </c>
+      <c r="B178" s="12">
+        <v>621308</v>
+      </c>
+      <c r="C178" s="14" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A179">
+        <v>50000416</v>
+      </c>
+      <c r="B179" s="12">
+        <v>1001122</v>
+      </c>
+      <c r="C179" s="13" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A180">
+        <v>50000416</v>
+      </c>
+      <c r="B180" s="12">
+        <v>1001126</v>
+      </c>
+      <c r="C180" s="13" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A181">
+        <v>50000416</v>
+      </c>
+      <c r="B181" s="12">
+        <v>1001004</v>
+      </c>
+      <c r="C181" s="14" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A182">
+        <v>50000416</v>
+      </c>
+      <c r="B182" s="12">
+        <v>346002</v>
+      </c>
+      <c r="C182" s="13" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A183">
+        <v>50000416</v>
+      </c>
+      <c r="B183" s="15">
+        <v>1001854</v>
+      </c>
+      <c r="C183" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A184">
+        <v>50000416</v>
+      </c>
+      <c r="B184" s="15">
+        <v>1002307</v>
+      </c>
+      <c r="C184" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A185">
+        <v>50000416</v>
+      </c>
+      <c r="B185" s="15">
+        <v>1002361</v>
+      </c>
+      <c r="C185" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A186">
+        <v>50000416</v>
+      </c>
+      <c r="B186" s="15">
+        <v>621888</v>
+      </c>
+      <c r="C186" t="s">
+        <v>289</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K98" xr:uid="{F1E63F05-B3C2-4FFE-ACBF-95CFEEB9BDFD}"/>
+  <conditionalFormatting sqref="B99:B186">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/clientes.xlsx
+++ b/clientes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lmacias\Desktop\RUTAS LÓGICAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87B49469-3C53-4501-A467-1592618A5E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85429251-68BA-4644-B63D-1F6AB13B7E50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{740DF47F-2FF5-45E2-939D-94824F9E772D}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="291">
   <si>
     <t>XIMENA SARAHI LOPEZ VILLASEÑOR</t>
   </si>
@@ -910,6 +910,9 @@
   </si>
   <si>
     <t>YASBEL GUADALUPE OCHOA DIAZ</t>
+  </si>
+  <si>
+    <t>CALLE 22 2610 COLON INDUSTRIAL 44940 GUADALAJARA JALISCO</t>
   </si>
 </sst>
 </file>
@@ -920,7 +923,7 @@
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0000000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -939,6 +942,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -980,7 +990,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1007,6 +1017,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -4601,6 +4615,28 @@
       <c r="C99" s="13" t="s">
         <v>202</v>
       </c>
+      <c r="D99" s="16">
+        <v>0</v>
+      </c>
+      <c r="E99" s="17"/>
+      <c r="F99" s="18">
+        <v>0</v>
+      </c>
+      <c r="G99" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H99" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I99" s="17">
+        <v>0</v>
+      </c>
+      <c r="J99" s="17">
+        <v>0</v>
+      </c>
+      <c r="K99" s="17" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A100">
@@ -4612,6 +4648,28 @@
       <c r="C100" s="13" t="s">
         <v>203</v>
       </c>
+      <c r="D100" s="16">
+        <v>0</v>
+      </c>
+      <c r="E100" s="17"/>
+      <c r="F100" s="18">
+        <v>0</v>
+      </c>
+      <c r="G100" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H100" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I100" s="17">
+        <v>0</v>
+      </c>
+      <c r="J100" s="17">
+        <v>0</v>
+      </c>
+      <c r="K100" s="17" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A101">
@@ -4623,6 +4681,28 @@
       <c r="C101" s="13" t="s">
         <v>204</v>
       </c>
+      <c r="D101" s="16">
+        <v>0</v>
+      </c>
+      <c r="E101" s="17"/>
+      <c r="F101" s="18">
+        <v>0</v>
+      </c>
+      <c r="G101" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H101" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I101" s="17">
+        <v>0</v>
+      </c>
+      <c r="J101" s="17">
+        <v>0</v>
+      </c>
+      <c r="K101" s="17" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A102">
@@ -4634,6 +4714,28 @@
       <c r="C102" s="13" t="s">
         <v>205</v>
       </c>
+      <c r="D102" s="16">
+        <v>0</v>
+      </c>
+      <c r="E102" s="17"/>
+      <c r="F102" s="18">
+        <v>0</v>
+      </c>
+      <c r="G102" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H102" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I102" s="17">
+        <v>0</v>
+      </c>
+      <c r="J102" s="17">
+        <v>0</v>
+      </c>
+      <c r="K102" s="17" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A103">
@@ -4645,6 +4747,28 @@
       <c r="C103" s="14" t="s">
         <v>206</v>
       </c>
+      <c r="D103" s="16">
+        <v>0</v>
+      </c>
+      <c r="E103" s="17"/>
+      <c r="F103" s="18">
+        <v>0</v>
+      </c>
+      <c r="G103" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H103" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I103" s="17">
+        <v>0</v>
+      </c>
+      <c r="J103" s="17">
+        <v>0</v>
+      </c>
+      <c r="K103" s="17" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A104">
@@ -4656,6 +4780,28 @@
       <c r="C104" s="14" t="s">
         <v>207</v>
       </c>
+      <c r="D104" s="16">
+        <v>0</v>
+      </c>
+      <c r="E104" s="17"/>
+      <c r="F104" s="18">
+        <v>0</v>
+      </c>
+      <c r="G104" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H104" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I104" s="17">
+        <v>0</v>
+      </c>
+      <c r="J104" s="17">
+        <v>0</v>
+      </c>
+      <c r="K104" s="17" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A105">
@@ -4667,6 +4813,28 @@
       <c r="C105" s="13" t="s">
         <v>208</v>
       </c>
+      <c r="D105" s="16">
+        <v>0</v>
+      </c>
+      <c r="E105" s="17"/>
+      <c r="F105" s="18">
+        <v>0</v>
+      </c>
+      <c r="G105" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H105" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I105" s="17">
+        <v>0</v>
+      </c>
+      <c r="J105" s="17">
+        <v>0</v>
+      </c>
+      <c r="K105" s="17" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A106">
@@ -4678,6 +4846,28 @@
       <c r="C106" s="13" t="s">
         <v>209</v>
       </c>
+      <c r="D106" s="16">
+        <v>0</v>
+      </c>
+      <c r="E106" s="17"/>
+      <c r="F106" s="18">
+        <v>0</v>
+      </c>
+      <c r="G106" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H106" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I106" s="17">
+        <v>0</v>
+      </c>
+      <c r="J106" s="17">
+        <v>0</v>
+      </c>
+      <c r="K106" s="17" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A107">
@@ -4689,6 +4879,28 @@
       <c r="C107" s="13" t="s">
         <v>210</v>
       </c>
+      <c r="D107" s="16">
+        <v>0</v>
+      </c>
+      <c r="E107" s="17"/>
+      <c r="F107" s="18">
+        <v>0</v>
+      </c>
+      <c r="G107" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H107" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I107" s="17">
+        <v>0</v>
+      </c>
+      <c r="J107" s="17">
+        <v>0</v>
+      </c>
+      <c r="K107" s="17" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A108">
@@ -4700,6 +4912,28 @@
       <c r="C108" s="14" t="s">
         <v>211</v>
       </c>
+      <c r="D108" s="16">
+        <v>0</v>
+      </c>
+      <c r="E108" s="17"/>
+      <c r="F108" s="18">
+        <v>0</v>
+      </c>
+      <c r="G108" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H108" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I108" s="17">
+        <v>0</v>
+      </c>
+      <c r="J108" s="17">
+        <v>0</v>
+      </c>
+      <c r="K108" s="17" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A109">
@@ -4711,6 +4945,28 @@
       <c r="C109" s="14" t="s">
         <v>212</v>
       </c>
+      <c r="D109" s="16">
+        <v>0</v>
+      </c>
+      <c r="E109" s="17"/>
+      <c r="F109" s="18">
+        <v>0</v>
+      </c>
+      <c r="G109" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H109" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I109" s="17">
+        <v>0</v>
+      </c>
+      <c r="J109" s="17">
+        <v>0</v>
+      </c>
+      <c r="K109" s="17" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A110">
@@ -4722,6 +4978,28 @@
       <c r="C110" s="14" t="s">
         <v>213</v>
       </c>
+      <c r="D110" s="16">
+        <v>0</v>
+      </c>
+      <c r="E110" s="17"/>
+      <c r="F110" s="18">
+        <v>0</v>
+      </c>
+      <c r="G110" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H110" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I110" s="17">
+        <v>0</v>
+      </c>
+      <c r="J110" s="17">
+        <v>0</v>
+      </c>
+      <c r="K110" s="17" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A111">
@@ -4733,6 +5011,28 @@
       <c r="C111" s="14" t="s">
         <v>214</v>
       </c>
+      <c r="D111" s="16">
+        <v>0</v>
+      </c>
+      <c r="E111" s="17"/>
+      <c r="F111" s="18">
+        <v>0</v>
+      </c>
+      <c r="G111" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H111" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I111" s="17">
+        <v>0</v>
+      </c>
+      <c r="J111" s="17">
+        <v>0</v>
+      </c>
+      <c r="K111" s="17" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A112">
@@ -4744,8 +5044,30 @@
       <c r="C112" s="14" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D112" s="16">
+        <v>0</v>
+      </c>
+      <c r="E112" s="17"/>
+      <c r="F112" s="18">
+        <v>0</v>
+      </c>
+      <c r="G112" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H112" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I112" s="17">
+        <v>0</v>
+      </c>
+      <c r="J112" s="17">
+        <v>0</v>
+      </c>
+      <c r="K112" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>50000416</v>
       </c>
@@ -4755,8 +5077,30 @@
       <c r="C113" s="14" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D113" s="16">
+        <v>0</v>
+      </c>
+      <c r="E113" s="17"/>
+      <c r="F113" s="18">
+        <v>0</v>
+      </c>
+      <c r="G113" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H113" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I113" s="17">
+        <v>0</v>
+      </c>
+      <c r="J113" s="17">
+        <v>0</v>
+      </c>
+      <c r="K113" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>50000416</v>
       </c>
@@ -4766,8 +5110,30 @@
       <c r="C114" s="14" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D114" s="16">
+        <v>0</v>
+      </c>
+      <c r="E114" s="17"/>
+      <c r="F114" s="18">
+        <v>0</v>
+      </c>
+      <c r="G114" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H114" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I114" s="17">
+        <v>0</v>
+      </c>
+      <c r="J114" s="17">
+        <v>0</v>
+      </c>
+      <c r="K114" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>50000416</v>
       </c>
@@ -4777,8 +5143,30 @@
       <c r="C115" s="13" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D115" s="16">
+        <v>0</v>
+      </c>
+      <c r="E115" s="17"/>
+      <c r="F115" s="18">
+        <v>0</v>
+      </c>
+      <c r="G115" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H115" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I115" s="17">
+        <v>0</v>
+      </c>
+      <c r="J115" s="17">
+        <v>0</v>
+      </c>
+      <c r="K115" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>50000416</v>
       </c>
@@ -4788,8 +5176,30 @@
       <c r="C116" s="13" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D116" s="16">
+        <v>0</v>
+      </c>
+      <c r="E116" s="17"/>
+      <c r="F116" s="18">
+        <v>0</v>
+      </c>
+      <c r="G116" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H116" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I116" s="17">
+        <v>0</v>
+      </c>
+      <c r="J116" s="17">
+        <v>0</v>
+      </c>
+      <c r="K116" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>50000416</v>
       </c>
@@ -4799,8 +5209,30 @@
       <c r="C117" s="14" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D117" s="16">
+        <v>0</v>
+      </c>
+      <c r="E117" s="17"/>
+      <c r="F117" s="18">
+        <v>0</v>
+      </c>
+      <c r="G117" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H117" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I117" s="17">
+        <v>0</v>
+      </c>
+      <c r="J117" s="17">
+        <v>0</v>
+      </c>
+      <c r="K117" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>50000416</v>
       </c>
@@ -4810,8 +5242,30 @@
       <c r="C118" s="14" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D118" s="16">
+        <v>0</v>
+      </c>
+      <c r="E118" s="17"/>
+      <c r="F118" s="18">
+        <v>0</v>
+      </c>
+      <c r="G118" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H118" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I118" s="17">
+        <v>0</v>
+      </c>
+      <c r="J118" s="17">
+        <v>0</v>
+      </c>
+      <c r="K118" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>50000416</v>
       </c>
@@ -4821,8 +5275,30 @@
       <c r="C119" s="13" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D119" s="16">
+        <v>0</v>
+      </c>
+      <c r="E119" s="17"/>
+      <c r="F119" s="18">
+        <v>0</v>
+      </c>
+      <c r="G119" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H119" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I119" s="17">
+        <v>0</v>
+      </c>
+      <c r="J119" s="17">
+        <v>0</v>
+      </c>
+      <c r="K119" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>50000416</v>
       </c>
@@ -4832,8 +5308,30 @@
       <c r="C120" s="14" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D120" s="16">
+        <v>0</v>
+      </c>
+      <c r="E120" s="17"/>
+      <c r="F120" s="18">
+        <v>0</v>
+      </c>
+      <c r="G120" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H120" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I120" s="17">
+        <v>0</v>
+      </c>
+      <c r="J120" s="17">
+        <v>0</v>
+      </c>
+      <c r="K120" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>50000416</v>
       </c>
@@ -4843,8 +5341,30 @@
       <c r="C121" s="14" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D121" s="16">
+        <v>0</v>
+      </c>
+      <c r="E121" s="17"/>
+      <c r="F121" s="18">
+        <v>0</v>
+      </c>
+      <c r="G121" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H121" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I121" s="17">
+        <v>0</v>
+      </c>
+      <c r="J121" s="17">
+        <v>0</v>
+      </c>
+      <c r="K121" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>50000416</v>
       </c>
@@ -4854,8 +5374,30 @@
       <c r="C122" s="14" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D122" s="16">
+        <v>0</v>
+      </c>
+      <c r="E122" s="17"/>
+      <c r="F122" s="18">
+        <v>0</v>
+      </c>
+      <c r="G122" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H122" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I122" s="17">
+        <v>0</v>
+      </c>
+      <c r="J122" s="17">
+        <v>0</v>
+      </c>
+      <c r="K122" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>50000416</v>
       </c>
@@ -4865,8 +5407,30 @@
       <c r="C123" s="13" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D123" s="16">
+        <v>0</v>
+      </c>
+      <c r="E123" s="17"/>
+      <c r="F123" s="18">
+        <v>0</v>
+      </c>
+      <c r="G123" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H123" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I123" s="17">
+        <v>0</v>
+      </c>
+      <c r="J123" s="17">
+        <v>0</v>
+      </c>
+      <c r="K123" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>50000416</v>
       </c>
@@ -4876,8 +5440,30 @@
       <c r="C124" s="13" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D124" s="16">
+        <v>0</v>
+      </c>
+      <c r="E124" s="17"/>
+      <c r="F124" s="18">
+        <v>0</v>
+      </c>
+      <c r="G124" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H124" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I124" s="17">
+        <v>0</v>
+      </c>
+      <c r="J124" s="17">
+        <v>0</v>
+      </c>
+      <c r="K124" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>50000416</v>
       </c>
@@ -4887,8 +5473,30 @@
       <c r="C125" s="13" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D125" s="16">
+        <v>0</v>
+      </c>
+      <c r="E125" s="17"/>
+      <c r="F125" s="18">
+        <v>0</v>
+      </c>
+      <c r="G125" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H125" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I125" s="17">
+        <v>0</v>
+      </c>
+      <c r="J125" s="17">
+        <v>0</v>
+      </c>
+      <c r="K125" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>50000416</v>
       </c>
@@ -4898,8 +5506,30 @@
       <c r="C126" s="13" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D126" s="16">
+        <v>0</v>
+      </c>
+      <c r="E126" s="17"/>
+      <c r="F126" s="18">
+        <v>0</v>
+      </c>
+      <c r="G126" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H126" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I126" s="17">
+        <v>0</v>
+      </c>
+      <c r="J126" s="17">
+        <v>0</v>
+      </c>
+      <c r="K126" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>50000416</v>
       </c>
@@ -4909,8 +5539,30 @@
       <c r="C127" s="13" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D127" s="16">
+        <v>0</v>
+      </c>
+      <c r="E127" s="17"/>
+      <c r="F127" s="18">
+        <v>0</v>
+      </c>
+      <c r="G127" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H127" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I127" s="17">
+        <v>0</v>
+      </c>
+      <c r="J127" s="17">
+        <v>0</v>
+      </c>
+      <c r="K127" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>50000416</v>
       </c>
@@ -4920,8 +5572,30 @@
       <c r="C128" s="14" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D128" s="16">
+        <v>0</v>
+      </c>
+      <c r="E128" s="17"/>
+      <c r="F128" s="18">
+        <v>0</v>
+      </c>
+      <c r="G128" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H128" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I128" s="17">
+        <v>0</v>
+      </c>
+      <c r="J128" s="17">
+        <v>0</v>
+      </c>
+      <c r="K128" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>50000416</v>
       </c>
@@ -4931,8 +5605,30 @@
       <c r="C129" s="14" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D129" s="16">
+        <v>0</v>
+      </c>
+      <c r="E129" s="17"/>
+      <c r="F129" s="18">
+        <v>0</v>
+      </c>
+      <c r="G129" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H129" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I129" s="17">
+        <v>0</v>
+      </c>
+      <c r="J129" s="17">
+        <v>0</v>
+      </c>
+      <c r="K129" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>50000416</v>
       </c>
@@ -4942,8 +5638,30 @@
       <c r="C130" s="14" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D130" s="16">
+        <v>0</v>
+      </c>
+      <c r="E130" s="17"/>
+      <c r="F130" s="18">
+        <v>0</v>
+      </c>
+      <c r="G130" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H130" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I130" s="17">
+        <v>0</v>
+      </c>
+      <c r="J130" s="17">
+        <v>0</v>
+      </c>
+      <c r="K130" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>50000416</v>
       </c>
@@ -4953,8 +5671,30 @@
       <c r="C131" s="13" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D131" s="16">
+        <v>0</v>
+      </c>
+      <c r="E131" s="17"/>
+      <c r="F131" s="18">
+        <v>0</v>
+      </c>
+      <c r="G131" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H131" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I131" s="17">
+        <v>0</v>
+      </c>
+      <c r="J131" s="17">
+        <v>0</v>
+      </c>
+      <c r="K131" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>50000416</v>
       </c>
@@ -4964,8 +5704,30 @@
       <c r="C132" s="13" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D132" s="16">
+        <v>0</v>
+      </c>
+      <c r="E132" s="17"/>
+      <c r="F132" s="18">
+        <v>0</v>
+      </c>
+      <c r="G132" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H132" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I132" s="17">
+        <v>0</v>
+      </c>
+      <c r="J132" s="17">
+        <v>0</v>
+      </c>
+      <c r="K132" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>50000416</v>
       </c>
@@ -4975,8 +5737,30 @@
       <c r="C133" s="14" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D133" s="16">
+        <v>0</v>
+      </c>
+      <c r="E133" s="17"/>
+      <c r="F133" s="18">
+        <v>0</v>
+      </c>
+      <c r="G133" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H133" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I133" s="17">
+        <v>0</v>
+      </c>
+      <c r="J133" s="17">
+        <v>0</v>
+      </c>
+      <c r="K133" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>50000416</v>
       </c>
@@ -4986,8 +5770,30 @@
       <c r="C134" s="14" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D134" s="16">
+        <v>0</v>
+      </c>
+      <c r="E134" s="17"/>
+      <c r="F134" s="18">
+        <v>0</v>
+      </c>
+      <c r="G134" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H134" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I134" s="17">
+        <v>0</v>
+      </c>
+      <c r="J134" s="17">
+        <v>0</v>
+      </c>
+      <c r="K134" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>50000416</v>
       </c>
@@ -4997,8 +5803,30 @@
       <c r="C135" s="14" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D135" s="16">
+        <v>0</v>
+      </c>
+      <c r="E135" s="17"/>
+      <c r="F135" s="18">
+        <v>0</v>
+      </c>
+      <c r="G135" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H135" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I135" s="17">
+        <v>0</v>
+      </c>
+      <c r="J135" s="17">
+        <v>0</v>
+      </c>
+      <c r="K135" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>50000416</v>
       </c>
@@ -5008,8 +5836,30 @@
       <c r="C136" s="13" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D136" s="16">
+        <v>0</v>
+      </c>
+      <c r="E136" s="17"/>
+      <c r="F136" s="18">
+        <v>0</v>
+      </c>
+      <c r="G136" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H136" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I136" s="17">
+        <v>0</v>
+      </c>
+      <c r="J136" s="17">
+        <v>0</v>
+      </c>
+      <c r="K136" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>50000416</v>
       </c>
@@ -5019,8 +5869,30 @@
       <c r="C137" s="14" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D137" s="16">
+        <v>0</v>
+      </c>
+      <c r="E137" s="17"/>
+      <c r="F137" s="18">
+        <v>0</v>
+      </c>
+      <c r="G137" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H137" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I137" s="17">
+        <v>0</v>
+      </c>
+      <c r="J137" s="17">
+        <v>0</v>
+      </c>
+      <c r="K137" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>50000416</v>
       </c>
@@ -5030,8 +5902,30 @@
       <c r="C138" s="14" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D138" s="16">
+        <v>0</v>
+      </c>
+      <c r="E138" s="17"/>
+      <c r="F138" s="18">
+        <v>0</v>
+      </c>
+      <c r="G138" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H138" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I138" s="17">
+        <v>0</v>
+      </c>
+      <c r="J138" s="17">
+        <v>0</v>
+      </c>
+      <c r="K138" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>50000416</v>
       </c>
@@ -5041,8 +5935,30 @@
       <c r="C139" s="14" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D139" s="16">
+        <v>0</v>
+      </c>
+      <c r="E139" s="17"/>
+      <c r="F139" s="18">
+        <v>0</v>
+      </c>
+      <c r="G139" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H139" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I139" s="17">
+        <v>0</v>
+      </c>
+      <c r="J139" s="17">
+        <v>0</v>
+      </c>
+      <c r="K139" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>50000416</v>
       </c>
@@ -5052,8 +5968,30 @@
       <c r="C140" s="14" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D140" s="16">
+        <v>0</v>
+      </c>
+      <c r="E140" s="17"/>
+      <c r="F140" s="18">
+        <v>0</v>
+      </c>
+      <c r="G140" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H140" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I140" s="17">
+        <v>0</v>
+      </c>
+      <c r="J140" s="17">
+        <v>0</v>
+      </c>
+      <c r="K140" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>50000416</v>
       </c>
@@ -5063,8 +6001,30 @@
       <c r="C141" s="14" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D141" s="16">
+        <v>0</v>
+      </c>
+      <c r="E141" s="17"/>
+      <c r="F141" s="18">
+        <v>0</v>
+      </c>
+      <c r="G141" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H141" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I141" s="17">
+        <v>0</v>
+      </c>
+      <c r="J141" s="17">
+        <v>0</v>
+      </c>
+      <c r="K141" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>50000416</v>
       </c>
@@ -5074,8 +6034,30 @@
       <c r="C142" s="14" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D142" s="16">
+        <v>0</v>
+      </c>
+      <c r="E142" s="17"/>
+      <c r="F142" s="18">
+        <v>0</v>
+      </c>
+      <c r="G142" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H142" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I142" s="17">
+        <v>0</v>
+      </c>
+      <c r="J142" s="17">
+        <v>0</v>
+      </c>
+      <c r="K142" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>50000416</v>
       </c>
@@ -5085,8 +6067,30 @@
       <c r="C143" s="14" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D143" s="16">
+        <v>0</v>
+      </c>
+      <c r="E143" s="17"/>
+      <c r="F143" s="18">
+        <v>0</v>
+      </c>
+      <c r="G143" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H143" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I143" s="17">
+        <v>0</v>
+      </c>
+      <c r="J143" s="17">
+        <v>0</v>
+      </c>
+      <c r="K143" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>50000416</v>
       </c>
@@ -5096,8 +6100,30 @@
       <c r="C144" s="14" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D144" s="16">
+        <v>0</v>
+      </c>
+      <c r="E144" s="17"/>
+      <c r="F144" s="18">
+        <v>0</v>
+      </c>
+      <c r="G144" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H144" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I144" s="17">
+        <v>0</v>
+      </c>
+      <c r="J144" s="17">
+        <v>0</v>
+      </c>
+      <c r="K144" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>50000416</v>
       </c>
@@ -5107,8 +6133,30 @@
       <c r="C145" s="14" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D145" s="16">
+        <v>0</v>
+      </c>
+      <c r="E145" s="17"/>
+      <c r="F145" s="18">
+        <v>0</v>
+      </c>
+      <c r="G145" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H145" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I145" s="17">
+        <v>0</v>
+      </c>
+      <c r="J145" s="17">
+        <v>0</v>
+      </c>
+      <c r="K145" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>50000416</v>
       </c>
@@ -5118,8 +6166,30 @@
       <c r="C146" s="14" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D146" s="16">
+        <v>0</v>
+      </c>
+      <c r="E146" s="17"/>
+      <c r="F146" s="18">
+        <v>0</v>
+      </c>
+      <c r="G146" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H146" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I146" s="17">
+        <v>0</v>
+      </c>
+      <c r="J146" s="17">
+        <v>0</v>
+      </c>
+      <c r="K146" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>50000416</v>
       </c>
@@ -5129,8 +6199,30 @@
       <c r="C147" s="14" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D147" s="16">
+        <v>0</v>
+      </c>
+      <c r="E147" s="17"/>
+      <c r="F147" s="18">
+        <v>0</v>
+      </c>
+      <c r="G147" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H147" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I147" s="17">
+        <v>0</v>
+      </c>
+      <c r="J147" s="17">
+        <v>0</v>
+      </c>
+      <c r="K147" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>50000416</v>
       </c>
@@ -5140,8 +6232,30 @@
       <c r="C148" s="14" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D148" s="16">
+        <v>0</v>
+      </c>
+      <c r="E148" s="17"/>
+      <c r="F148" s="18">
+        <v>0</v>
+      </c>
+      <c r="G148" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H148" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I148" s="17">
+        <v>0</v>
+      </c>
+      <c r="J148" s="17">
+        <v>0</v>
+      </c>
+      <c r="K148" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>50000416</v>
       </c>
@@ -5151,8 +6265,30 @@
       <c r="C149" s="13" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D149" s="16">
+        <v>0</v>
+      </c>
+      <c r="E149" s="17"/>
+      <c r="F149" s="18">
+        <v>0</v>
+      </c>
+      <c r="G149" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H149" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I149" s="17">
+        <v>0</v>
+      </c>
+      <c r="J149" s="17">
+        <v>0</v>
+      </c>
+      <c r="K149" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>50000416</v>
       </c>
@@ -5162,8 +6298,30 @@
       <c r="C150" s="13" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D150" s="16">
+        <v>0</v>
+      </c>
+      <c r="E150" s="17"/>
+      <c r="F150" s="18">
+        <v>0</v>
+      </c>
+      <c r="G150" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H150" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I150" s="17">
+        <v>0</v>
+      </c>
+      <c r="J150" s="17">
+        <v>0</v>
+      </c>
+      <c r="K150" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>50000416</v>
       </c>
@@ -5173,8 +6331,30 @@
       <c r="C151" s="14" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D151" s="16">
+        <v>0</v>
+      </c>
+      <c r="E151" s="17"/>
+      <c r="F151" s="18">
+        <v>0</v>
+      </c>
+      <c r="G151" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H151" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I151" s="17">
+        <v>0</v>
+      </c>
+      <c r="J151" s="17">
+        <v>0</v>
+      </c>
+      <c r="K151" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>50000416</v>
       </c>
@@ -5184,8 +6364,30 @@
       <c r="C152" s="13" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D152" s="16">
+        <v>0</v>
+      </c>
+      <c r="E152" s="17"/>
+      <c r="F152" s="18">
+        <v>0</v>
+      </c>
+      <c r="G152" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H152" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I152" s="17">
+        <v>0</v>
+      </c>
+      <c r="J152" s="17">
+        <v>0</v>
+      </c>
+      <c r="K152" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A153">
         <v>50000416</v>
       </c>
@@ -5195,8 +6397,30 @@
       <c r="C153" s="14" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D153" s="16">
+        <v>0</v>
+      </c>
+      <c r="E153" s="17"/>
+      <c r="F153" s="18">
+        <v>0</v>
+      </c>
+      <c r="G153" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H153" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I153" s="17">
+        <v>0</v>
+      </c>
+      <c r="J153" s="17">
+        <v>0</v>
+      </c>
+      <c r="K153" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>50000416</v>
       </c>
@@ -5206,8 +6430,30 @@
       <c r="C154" s="14" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D154" s="16">
+        <v>0</v>
+      </c>
+      <c r="E154" s="17"/>
+      <c r="F154" s="18">
+        <v>0</v>
+      </c>
+      <c r="G154" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H154" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I154" s="17">
+        <v>0</v>
+      </c>
+      <c r="J154" s="17">
+        <v>0</v>
+      </c>
+      <c r="K154" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A155">
         <v>50000416</v>
       </c>
@@ -5217,8 +6463,30 @@
       <c r="C155" s="14" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D155" s="16">
+        <v>0</v>
+      </c>
+      <c r="E155" s="17"/>
+      <c r="F155" s="18">
+        <v>0</v>
+      </c>
+      <c r="G155" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H155" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I155" s="17">
+        <v>0</v>
+      </c>
+      <c r="J155" s="17">
+        <v>0</v>
+      </c>
+      <c r="K155" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A156">
         <v>50000416</v>
       </c>
@@ -5228,8 +6496,30 @@
       <c r="C156" s="14" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D156" s="16">
+        <v>0</v>
+      </c>
+      <c r="E156" s="17"/>
+      <c r="F156" s="18">
+        <v>0</v>
+      </c>
+      <c r="G156" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H156" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I156" s="17">
+        <v>0</v>
+      </c>
+      <c r="J156" s="17">
+        <v>0</v>
+      </c>
+      <c r="K156" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A157">
         <v>50000416</v>
       </c>
@@ -5239,8 +6529,30 @@
       <c r="C157" s="14" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D157" s="16">
+        <v>0</v>
+      </c>
+      <c r="E157" s="17"/>
+      <c r="F157" s="18">
+        <v>0</v>
+      </c>
+      <c r="G157" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H157" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I157" s="17">
+        <v>0</v>
+      </c>
+      <c r="J157" s="17">
+        <v>0</v>
+      </c>
+      <c r="K157" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A158">
         <v>50000416</v>
       </c>
@@ -5250,8 +6562,30 @@
       <c r="C158" s="14" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D158" s="16">
+        <v>0</v>
+      </c>
+      <c r="E158" s="17"/>
+      <c r="F158" s="18">
+        <v>0</v>
+      </c>
+      <c r="G158" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H158" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I158" s="17">
+        <v>0</v>
+      </c>
+      <c r="J158" s="17">
+        <v>0</v>
+      </c>
+      <c r="K158" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="159" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>50000416</v>
       </c>
@@ -5261,8 +6595,30 @@
       <c r="C159" s="14" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D159" s="16">
+        <v>0</v>
+      </c>
+      <c r="E159" s="17"/>
+      <c r="F159" s="18">
+        <v>0</v>
+      </c>
+      <c r="G159" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H159" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I159" s="17">
+        <v>0</v>
+      </c>
+      <c r="J159" s="17">
+        <v>0</v>
+      </c>
+      <c r="K159" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="160" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A160">
         <v>50000416</v>
       </c>
@@ -5272,8 +6628,30 @@
       <c r="C160" s="14" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D160" s="16">
+        <v>0</v>
+      </c>
+      <c r="E160" s="17"/>
+      <c r="F160" s="18">
+        <v>0</v>
+      </c>
+      <c r="G160" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H160" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I160" s="17">
+        <v>0</v>
+      </c>
+      <c r="J160" s="17">
+        <v>0</v>
+      </c>
+      <c r="K160" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="161" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>50000416</v>
       </c>
@@ -5283,8 +6661,30 @@
       <c r="C161" s="13" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D161" s="16">
+        <v>0</v>
+      </c>
+      <c r="E161" s="17"/>
+      <c r="F161" s="18">
+        <v>0</v>
+      </c>
+      <c r="G161" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H161" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I161" s="17">
+        <v>0</v>
+      </c>
+      <c r="J161" s="17">
+        <v>0</v>
+      </c>
+      <c r="K161" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="162" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A162">
         <v>50000416</v>
       </c>
@@ -5294,8 +6694,30 @@
       <c r="C162" s="13" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D162" s="16">
+        <v>0</v>
+      </c>
+      <c r="E162" s="17"/>
+      <c r="F162" s="18">
+        <v>0</v>
+      </c>
+      <c r="G162" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H162" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I162" s="17">
+        <v>0</v>
+      </c>
+      <c r="J162" s="17">
+        <v>0</v>
+      </c>
+      <c r="K162" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="163" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A163">
         <v>50000416</v>
       </c>
@@ -5305,8 +6727,30 @@
       <c r="C163" s="14" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D163" s="16">
+        <v>0</v>
+      </c>
+      <c r="E163" s="17"/>
+      <c r="F163" s="18">
+        <v>0</v>
+      </c>
+      <c r="G163" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H163" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I163" s="17">
+        <v>0</v>
+      </c>
+      <c r="J163" s="17">
+        <v>0</v>
+      </c>
+      <c r="K163" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="164" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A164">
         <v>50000416</v>
       </c>
@@ -5316,8 +6760,30 @@
       <c r="C164" s="13" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D164" s="16">
+        <v>0</v>
+      </c>
+      <c r="E164" s="17"/>
+      <c r="F164" s="18">
+        <v>0</v>
+      </c>
+      <c r="G164" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H164" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I164" s="17">
+        <v>0</v>
+      </c>
+      <c r="J164" s="17">
+        <v>0</v>
+      </c>
+      <c r="K164" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A165">
         <v>50000416</v>
       </c>
@@ -5327,8 +6793,30 @@
       <c r="C165" s="13" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D165" s="16">
+        <v>0</v>
+      </c>
+      <c r="E165" s="17"/>
+      <c r="F165" s="18">
+        <v>0</v>
+      </c>
+      <c r="G165" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H165" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I165" s="17">
+        <v>0</v>
+      </c>
+      <c r="J165" s="17">
+        <v>0</v>
+      </c>
+      <c r="K165" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A166">
         <v>50000416</v>
       </c>
@@ -5338,8 +6826,30 @@
       <c r="C166" s="14" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D166" s="16">
+        <v>0</v>
+      </c>
+      <c r="E166" s="17"/>
+      <c r="F166" s="18">
+        <v>0</v>
+      </c>
+      <c r="G166" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H166" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I166" s="17">
+        <v>0</v>
+      </c>
+      <c r="J166" s="17">
+        <v>0</v>
+      </c>
+      <c r="K166" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="167" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A167">
         <v>50000416</v>
       </c>
@@ -5349,8 +6859,30 @@
       <c r="C167" s="14" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D167" s="16">
+        <v>0</v>
+      </c>
+      <c r="E167" s="17"/>
+      <c r="F167" s="18">
+        <v>0</v>
+      </c>
+      <c r="G167" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H167" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I167" s="17">
+        <v>0</v>
+      </c>
+      <c r="J167" s="17">
+        <v>0</v>
+      </c>
+      <c r="K167" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>50000416</v>
       </c>
@@ -5360,8 +6892,30 @@
       <c r="C168" s="14" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D168" s="16">
+        <v>0</v>
+      </c>
+      <c r="E168" s="17"/>
+      <c r="F168" s="18">
+        <v>0</v>
+      </c>
+      <c r="G168" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H168" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I168" s="17">
+        <v>0</v>
+      </c>
+      <c r="J168" s="17">
+        <v>0</v>
+      </c>
+      <c r="K168" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A169">
         <v>50000416</v>
       </c>
@@ -5371,8 +6925,30 @@
       <c r="C169" s="14" t="s">
         <v>272</v>
       </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D169" s="16">
+        <v>0</v>
+      </c>
+      <c r="E169" s="17"/>
+      <c r="F169" s="18">
+        <v>0</v>
+      </c>
+      <c r="G169" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H169" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I169" s="17">
+        <v>0</v>
+      </c>
+      <c r="J169" s="17">
+        <v>0</v>
+      </c>
+      <c r="K169" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A170">
         <v>50000416</v>
       </c>
@@ -5382,8 +6958,30 @@
       <c r="C170" s="14" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D170" s="16">
+        <v>0</v>
+      </c>
+      <c r="E170" s="17"/>
+      <c r="F170" s="18">
+        <v>0</v>
+      </c>
+      <c r="G170" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H170" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I170" s="17">
+        <v>0</v>
+      </c>
+      <c r="J170" s="17">
+        <v>0</v>
+      </c>
+      <c r="K170" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A171">
         <v>50000416</v>
       </c>
@@ -5393,8 +6991,30 @@
       <c r="C171" s="13" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D171" s="16">
+        <v>0</v>
+      </c>
+      <c r="E171" s="17"/>
+      <c r="F171" s="18">
+        <v>0</v>
+      </c>
+      <c r="G171" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H171" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I171" s="17">
+        <v>0</v>
+      </c>
+      <c r="J171" s="17">
+        <v>0</v>
+      </c>
+      <c r="K171" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="172" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A172">
         <v>50000416</v>
       </c>
@@ -5404,8 +7024,30 @@
       <c r="C172" s="14" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D172" s="16">
+        <v>0</v>
+      </c>
+      <c r="E172" s="17"/>
+      <c r="F172" s="18">
+        <v>0</v>
+      </c>
+      <c r="G172" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H172" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I172" s="17">
+        <v>0</v>
+      </c>
+      <c r="J172" s="17">
+        <v>0</v>
+      </c>
+      <c r="K172" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="173" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A173">
         <v>50000416</v>
       </c>
@@ -5415,8 +7057,30 @@
       <c r="C173" s="14" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D173" s="16">
+        <v>0</v>
+      </c>
+      <c r="E173" s="17"/>
+      <c r="F173" s="18">
+        <v>0</v>
+      </c>
+      <c r="G173" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H173" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I173" s="17">
+        <v>0</v>
+      </c>
+      <c r="J173" s="17">
+        <v>0</v>
+      </c>
+      <c r="K173" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A174">
         <v>50000416</v>
       </c>
@@ -5426,8 +7090,30 @@
       <c r="C174" s="13" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D174" s="16">
+        <v>0</v>
+      </c>
+      <c r="E174" s="17"/>
+      <c r="F174" s="18">
+        <v>0</v>
+      </c>
+      <c r="G174" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H174" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I174" s="17">
+        <v>0</v>
+      </c>
+      <c r="J174" s="17">
+        <v>0</v>
+      </c>
+      <c r="K174" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="175" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A175">
         <v>50000416</v>
       </c>
@@ -5437,8 +7123,30 @@
       <c r="C175" s="14" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D175" s="16">
+        <v>0</v>
+      </c>
+      <c r="E175" s="17"/>
+      <c r="F175" s="18">
+        <v>0</v>
+      </c>
+      <c r="G175" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H175" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I175" s="17">
+        <v>0</v>
+      </c>
+      <c r="J175" s="17">
+        <v>0</v>
+      </c>
+      <c r="K175" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="176" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A176">
         <v>50000416</v>
       </c>
@@ -5448,8 +7156,30 @@
       <c r="C176" s="14" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D176" s="16">
+        <v>0</v>
+      </c>
+      <c r="E176" s="17"/>
+      <c r="F176" s="18">
+        <v>0</v>
+      </c>
+      <c r="G176" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H176" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I176" s="17">
+        <v>0</v>
+      </c>
+      <c r="J176" s="17">
+        <v>0</v>
+      </c>
+      <c r="K176" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="177" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A177">
         <v>50000416</v>
       </c>
@@ -5459,8 +7189,30 @@
       <c r="C177" s="13" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D177" s="16">
+        <v>0</v>
+      </c>
+      <c r="E177" s="17"/>
+      <c r="F177" s="18">
+        <v>0</v>
+      </c>
+      <c r="G177" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H177" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I177" s="17">
+        <v>0</v>
+      </c>
+      <c r="J177" s="17">
+        <v>0</v>
+      </c>
+      <c r="K177" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="178" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A178">
         <v>50000416</v>
       </c>
@@ -5470,8 +7222,30 @@
       <c r="C178" s="14" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D178" s="16">
+        <v>0</v>
+      </c>
+      <c r="E178" s="17"/>
+      <c r="F178" s="18">
+        <v>0</v>
+      </c>
+      <c r="G178" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H178" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I178" s="17">
+        <v>0</v>
+      </c>
+      <c r="J178" s="17">
+        <v>0</v>
+      </c>
+      <c r="K178" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="179" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A179">
         <v>50000416</v>
       </c>
@@ -5481,8 +7255,30 @@
       <c r="C179" s="13" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D179" s="16">
+        <v>0</v>
+      </c>
+      <c r="E179" s="17"/>
+      <c r="F179" s="18">
+        <v>0</v>
+      </c>
+      <c r="G179" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H179" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I179" s="17">
+        <v>0</v>
+      </c>
+      <c r="J179" s="17">
+        <v>0</v>
+      </c>
+      <c r="K179" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="180" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A180">
         <v>50000416</v>
       </c>
@@ -5492,8 +7288,30 @@
       <c r="C180" s="13" t="s">
         <v>283</v>
       </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D180" s="16">
+        <v>0</v>
+      </c>
+      <c r="E180" s="17"/>
+      <c r="F180" s="18">
+        <v>0</v>
+      </c>
+      <c r="G180" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H180" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I180" s="17">
+        <v>0</v>
+      </c>
+      <c r="J180" s="17">
+        <v>0</v>
+      </c>
+      <c r="K180" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="181" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A181">
         <v>50000416</v>
       </c>
@@ -5503,8 +7321,30 @@
       <c r="C181" s="14" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D181" s="16">
+        <v>0</v>
+      </c>
+      <c r="E181" s="17"/>
+      <c r="F181" s="18">
+        <v>0</v>
+      </c>
+      <c r="G181" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H181" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I181" s="17">
+        <v>0</v>
+      </c>
+      <c r="J181" s="17">
+        <v>0</v>
+      </c>
+      <c r="K181" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="182" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A182">
         <v>50000416</v>
       </c>
@@ -5514,8 +7354,30 @@
       <c r="C182" s="13" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D182" s="16">
+        <v>0</v>
+      </c>
+      <c r="E182" s="17"/>
+      <c r="F182" s="18">
+        <v>0</v>
+      </c>
+      <c r="G182" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H182" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I182" s="17">
+        <v>0</v>
+      </c>
+      <c r="J182" s="17">
+        <v>0</v>
+      </c>
+      <c r="K182" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="183" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A183">
         <v>50000416</v>
       </c>
@@ -5525,8 +7387,30 @@
       <c r="C183" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D183" s="16">
+        <v>0</v>
+      </c>
+      <c r="E183" s="17"/>
+      <c r="F183" s="18">
+        <v>0</v>
+      </c>
+      <c r="G183" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H183" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I183" s="17">
+        <v>0</v>
+      </c>
+      <c r="J183" s="17">
+        <v>0</v>
+      </c>
+      <c r="K183" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="184" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A184">
         <v>50000416</v>
       </c>
@@ -5536,8 +7420,30 @@
       <c r="C184" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D184" s="16">
+        <v>0</v>
+      </c>
+      <c r="E184" s="17"/>
+      <c r="F184" s="18">
+        <v>0</v>
+      </c>
+      <c r="G184" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H184" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I184" s="17">
+        <v>0</v>
+      </c>
+      <c r="J184" s="17">
+        <v>0</v>
+      </c>
+      <c r="K184" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="185" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A185">
         <v>50000416</v>
       </c>
@@ -5547,8 +7453,30 @@
       <c r="C185" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D185" s="16">
+        <v>0</v>
+      </c>
+      <c r="E185" s="17"/>
+      <c r="F185" s="18">
+        <v>0</v>
+      </c>
+      <c r="G185" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H185" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I185" s="17">
+        <v>0</v>
+      </c>
+      <c r="J185" s="17">
+        <v>0</v>
+      </c>
+      <c r="K185" s="17" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="186" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A186">
         <v>50000416</v>
       </c>
@@ -5557,6 +7485,28 @@
       </c>
       <c r="C186" t="s">
         <v>289</v>
+      </c>
+      <c r="D186" s="16">
+        <v>0</v>
+      </c>
+      <c r="E186" s="17"/>
+      <c r="F186" s="18">
+        <v>0</v>
+      </c>
+      <c r="G186" s="19">
+        <v>20.6359613663865</v>
+      </c>
+      <c r="H186" s="19">
+        <v>-103.357484717212</v>
+      </c>
+      <c r="I186" s="17">
+        <v>0</v>
+      </c>
+      <c r="J186" s="17">
+        <v>0</v>
+      </c>
+      <c r="K186" s="17" t="s">
+        <v>290</v>
       </c>
     </row>
   </sheetData>
